--- a/diseases/d092/1995-1999.xlsx
+++ b/diseases/d092/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>84</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>35</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>78</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>46</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>89</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>39</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>85</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>47</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>132</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>54</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>211</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>87</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>505</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>194</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>306</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>221</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>175</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>121</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>246</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>95</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>177</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>53</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>108</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>43</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>112</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>48</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>93</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>37</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>147</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>40</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>189</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>44</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>168</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>62</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>208</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>74</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>546</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>181</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>353</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>239</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>196</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>172</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>239</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>100</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>223</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>69</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>155</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>76</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>133</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20500,9 +20353,6 @@
       <c r="O102" t="n">
         <v>41</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20893,9 +20743,6 @@
       <c r="O104" t="n">
         <v>116</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21525,9 +21372,6 @@
       <c r="O107" t="n">
         <v>40</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21918,9 +21762,6 @@
       <c r="O109" t="n">
         <v>169</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22550,9 +22391,6 @@
       <c r="O112" t="n">
         <v>49</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22943,9 +22781,6 @@
       <c r="O114" t="n">
         <v>183</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23575,9 +23410,6 @@
       <c r="O117" t="n">
         <v>67</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23968,9 +23800,6 @@
       <c r="O119" t="n">
         <v>132</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24600,9 +24429,6 @@
       <c r="O122" t="n">
         <v>58</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24993,9 +24819,6 @@
       <c r="O124" t="n">
         <v>179</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25625,9 +25448,6 @@
       <c r="O127" t="n">
         <v>113</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26018,9 +25838,6 @@
       <c r="O129" t="n">
         <v>440</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26650,9 +26467,6 @@
       <c r="O132" t="n">
         <v>230</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27043,9 +26857,6 @@
       <c r="O134" t="n">
         <v>345</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27675,9 +27486,6 @@
       <c r="O137" t="n">
         <v>201</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28068,9 +27876,6 @@
       <c r="O139" t="n">
         <v>217</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28700,9 +28505,6 @@
       <c r="O142" t="n">
         <v>119</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29093,9 +28895,6 @@
       <c r="O144" t="n">
         <v>195</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29725,9 +29524,6 @@
       <c r="O147" t="n">
         <v>114</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30118,9 +29914,6 @@
       <c r="O149" t="n">
         <v>137</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30750,9 +30543,6 @@
       <c r="O152" t="n">
         <v>69</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31143,9 +30933,6 @@
       <c r="O154" t="n">
         <v>115</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31775,9 +31562,6 @@
       <c r="O157" t="n">
         <v>66</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32168,9 +31952,6 @@
       <c r="O159" t="n">
         <v>125</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33039,9 +32820,6 @@
       <c r="O163" t="n">
         <v>53</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33432,9 +33210,6 @@
       <c r="O165" t="n">
         <v>80</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34064,9 +33839,6 @@
       <c r="O168" t="n">
         <v>58</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34457,9 +34229,6 @@
       <c r="O170" t="n">
         <v>121</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35089,9 +34858,6 @@
       <c r="O173" t="n">
         <v>69</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35482,9 +35248,6 @@
       <c r="O175" t="n">
         <v>131</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36114,9 +35877,6 @@
       <c r="O178" t="n">
         <v>92</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36507,9 +36267,6 @@
       <c r="O180" t="n">
         <v>196</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37139,9 +36896,6 @@
       <c r="O183" t="n">
         <v>75</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="S183" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37532,9 +37286,6 @@
       <c r="O185" t="n">
         <v>238</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38164,9 +37915,6 @@
       <c r="O188" t="n">
         <v>109</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38557,9 +38305,6 @@
       <c r="O190" t="n">
         <v>480</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39189,9 +38934,6 @@
       <c r="O193" t="n">
         <v>352</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39582,9 +39324,6 @@
       <c r="O195" t="n">
         <v>453</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40214,9 +39953,6 @@
       <c r="O198" t="n">
         <v>315</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40607,9 +40343,6 @@
       <c r="O200" t="n">
         <v>263</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41239,9 +40972,6 @@
       <c r="O203" t="n">
         <v>182</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41632,9 +41362,6 @@
       <c r="O205" t="n">
         <v>304</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42264,9 +41991,6 @@
       <c r="O208" t="n">
         <v>160</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42657,9 +42381,6 @@
       <c r="O210" t="n">
         <v>245</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43289,9 +43010,6 @@
       <c r="O213" t="n">
         <v>119</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43682,9 +43400,6 @@
       <c r="O215" t="n">
         <v>214</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44314,9 +44029,6 @@
       <c r="O218" t="n">
         <v>106</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44707,9 +44419,6 @@
       <c r="O220" t="n">
         <v>200</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45578,9 +45287,6 @@
       <c r="O224" t="n">
         <v>94</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45971,9 +45677,6 @@
       <c r="O226" t="n">
         <v>138</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46603,9 +46306,6 @@
       <c r="O229" t="n">
         <v>81</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46996,9 +46696,6 @@
       <c r="O231" t="n">
         <v>167</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47628,9 +47325,6 @@
       <c r="O234" t="n">
         <v>94</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48021,9 +47715,6 @@
       <c r="O236" t="n">
         <v>166</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48653,9 +48344,6 @@
       <c r="O239" t="n">
         <v>131</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49046,9 +48734,6 @@
       <c r="O241" t="n">
         <v>174</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49678,9 +49363,6 @@
       <c r="O244" t="n">
         <v>89</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50071,9 +49753,6 @@
       <c r="O246" t="n">
         <v>273</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50703,9 +50382,6 @@
       <c r="O249" t="n">
         <v>192</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51096,9 +50772,6 @@
       <c r="O251" t="n">
         <v>744</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51728,9 +51401,6 @@
       <c r="O254" t="n">
         <v>425</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52121,9 +51791,6 @@
       <c r="O256" t="n">
         <v>428</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52753,9 +52420,6 @@
       <c r="O259" t="n">
         <v>339</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53146,9 +52810,6 @@
       <c r="O261" t="n">
         <v>232</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53778,9 +53439,6 @@
       <c r="O264" t="n">
         <v>176</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54171,9 +53829,6 @@
       <c r="O266" t="n">
         <v>298</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54803,9 +54458,6 @@
       <c r="O269" t="n">
         <v>190</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55196,9 +54848,6 @@
       <c r="O271" t="n">
         <v>248</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55828,9 +55477,6 @@
       <c r="O274" t="n">
         <v>119</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56221,9 +55867,6 @@
       <c r="O276" t="n">
         <v>215</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56852,9 +56495,6 @@
       </c>
       <c r="O279" t="n">
         <v>110</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>0</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
